--- a/dataset/ERP System/Currency_Rate.xlsx
+++ b/dataset/ERP System/Currency_Rate.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\one\Deakin University\Course\T3\Enterprise Data Management\Assignment\MIS774-ICE-Entertainment-DW\dataset\ERP System\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B690D7-A9ED-4F4A-954C-6AA014763A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="8" windowWidth="24195" windowHeight="15195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -379,11 +385,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,13 +427,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -465,7 +479,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -499,6 +513,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -533,9 +548,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -708,11 +724,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E370"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -729,7 +751,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>44562</v>
       </c>
@@ -737,7 +759,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.641865</v>
+        <v>0.64186500000000002</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -746,7 +768,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>44592</v>
       </c>
@@ -754,7 +776,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>0.641797</v>
+        <v>0.64179699999999995</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -763,7 +785,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>44622</v>
       </c>
@@ -771,7 +793,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.630302</v>
+        <v>0.63030200000000003</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -780,7 +802,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>44652</v>
       </c>
@@ -788,7 +810,7 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>0.635996</v>
+        <v>0.63599600000000001</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -797,7 +819,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>44682</v>
       </c>
@@ -805,7 +827,7 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>0.63883</v>
+        <v>0.63883000000000001</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -814,7 +836,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>44712</v>
       </c>
@@ -822,7 +844,7 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>0.640595</v>
+        <v>0.64059500000000003</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -831,7 +853,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>44742</v>
       </c>
@@ -839,7 +861,7 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>0.632099</v>
+        <v>0.63209899999999997</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
@@ -848,7 +870,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>44772</v>
       </c>
@@ -865,7 +887,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>44802</v>
       </c>
@@ -873,7 +895,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>0.634665</v>
+        <v>0.63466500000000003</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
@@ -882,7 +904,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>44832</v>
       </c>
@@ -890,7 +912,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>0.634621</v>
+        <v>0.63462099999999999</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -899,7 +921,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>44862</v>
       </c>
@@ -907,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.6238629999999999</v>
+        <v>0.62386299999999995</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
@@ -916,7 +938,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>44892</v>
       </c>
@@ -924,7 +946,7 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>0.619083</v>
+        <v>0.61908300000000005</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -933,7 +955,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>44922</v>
       </c>
@@ -941,7 +963,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>0.62587</v>
+        <v>0.62587000000000004</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
@@ -950,7 +972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>44952</v>
       </c>
@@ -958,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>0.626146</v>
+        <v>0.62614599999999998</v>
       </c>
       <c r="D15" t="s">
         <v>27</v>
@@ -967,7 +989,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>44982</v>
       </c>
@@ -975,7 +997,7 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>0.631095</v>
+        <v>0.63109499999999996</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -984,7 +1006,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>45012</v>
       </c>
@@ -992,7 +1014,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>0.626939</v>
+        <v>0.62693900000000002</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
@@ -1001,7 +1023,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>45042</v>
       </c>
@@ -1009,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>0.6231139999999999</v>
+        <v>0.62311399999999995</v>
       </c>
       <c r="D18" t="s">
         <v>30</v>
@@ -1018,7 +1040,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>45072</v>
       </c>
@@ -1026,7 +1048,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>0.632783</v>
+        <v>0.63278299999999998</v>
       </c>
       <c r="D19" t="s">
         <v>31</v>
@@ -1035,7 +1057,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>45102</v>
       </c>
@@ -1043,7 +1065,7 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>0.636889</v>
+        <v>0.63688900000000004</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
@@ -1052,7 +1074,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>45132</v>
       </c>
@@ -1060,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>0.636265</v>
+        <v>0.63626499999999997</v>
       </c>
       <c r="D21" t="s">
         <v>33</v>
@@ -1069,7 +1091,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>45162</v>
       </c>
@@ -1077,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>0.644846</v>
+        <v>0.64484600000000003</v>
       </c>
       <c r="D22" t="s">
         <v>34</v>
@@ -1086,7 +1108,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>45192</v>
       </c>
@@ -1094,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="C23">
-        <v>0.637034</v>
+        <v>0.63703399999999999</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -1103,7 +1125,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>45222</v>
       </c>
@@ -1111,7 +1133,7 @@
         <v>7</v>
       </c>
       <c r="C24">
-        <v>0.639265</v>
+        <v>0.63926499999999997</v>
       </c>
       <c r="D24" t="s">
         <v>36</v>
@@ -1120,7 +1142,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>45252</v>
       </c>
@@ -1128,7 +1150,7 @@
         <v>7</v>
       </c>
       <c r="C25">
-        <v>0.627015</v>
+        <v>0.62701499999999999</v>
       </c>
       <c r="D25" t="s">
         <v>37</v>
@@ -1137,7 +1159,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>45282</v>
       </c>
@@ -1145,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="C26">
-        <v>0.630362</v>
+        <v>0.63036199999999998</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
@@ -1154,7 +1176,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>45312</v>
       </c>
@@ -1162,7 +1184,7 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>0.6316929999999999</v>
+        <v>0.63169299999999995</v>
       </c>
       <c r="D27" t="s">
         <v>39</v>
@@ -1171,7 +1193,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>45342</v>
       </c>
@@ -1179,7 +1201,7 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>0.636675</v>
+        <v>0.63667499999999999</v>
       </c>
       <c r="D28" t="s">
         <v>40</v>
@@ -1188,7 +1210,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>45372</v>
       </c>
@@ -1196,7 +1218,7 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>0.627035</v>
+        <v>0.62703500000000001</v>
       </c>
       <c r="D29" t="s">
         <v>41</v>
@@ -1205,7 +1227,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>45402</v>
       </c>
@@ -1222,7 +1244,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>45432</v>
       </c>
@@ -1230,7 +1252,7 @@
         <v>7</v>
       </c>
       <c r="C31">
-        <v>0.604701</v>
+        <v>0.60470100000000004</v>
       </c>
       <c r="D31" t="s">
         <v>43</v>
@@ -1239,7 +1261,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>45462</v>
       </c>
@@ -1247,7 +1269,7 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>0.609347</v>
+        <v>0.60934699999999997</v>
       </c>
       <c r="D32" t="s">
         <v>44</v>
@@ -1256,7 +1278,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>45492</v>
       </c>
@@ -1264,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>0.599922</v>
+        <v>0.59992199999999996</v>
       </c>
       <c r="D33" t="s">
         <v>45</v>
@@ -1273,7 +1295,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>45522</v>
       </c>
@@ -1281,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="C34">
-        <v>0.59209</v>
+        <v>0.59209000000000001</v>
       </c>
       <c r="D34" t="s">
         <v>46</v>
@@ -1290,7 +1312,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>45552</v>
       </c>
@@ -1298,7 +1320,7 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>0.596994</v>
+        <v>0.59699400000000002</v>
       </c>
       <c r="D35" t="s">
         <v>47</v>
@@ -1307,7 +1329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>45582</v>
       </c>
@@ -1315,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="C36">
-        <v>0.59378</v>
+        <v>0.59377999999999997</v>
       </c>
       <c r="D36" t="s">
         <v>48</v>
@@ -1324,7 +1346,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>45612</v>
       </c>
@@ -1332,7 +1354,7 @@
         <v>7</v>
       </c>
       <c r="C37">
-        <v>0.59611</v>
+        <v>0.59611000000000003</v>
       </c>
       <c r="D37" t="s">
         <v>49</v>
@@ -1341,7 +1363,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>45642</v>
       </c>
@@ -1349,7 +1371,7 @@
         <v>7</v>
       </c>
       <c r="C38">
-        <v>0.595903</v>
+        <v>0.59590299999999996</v>
       </c>
       <c r="D38" t="s">
         <v>50</v>
@@ -1358,7 +1380,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>45672</v>
       </c>
@@ -1366,7 +1388,7 @@
         <v>7</v>
       </c>
       <c r="C39">
-        <v>0.585634</v>
+        <v>0.58563399999999999</v>
       </c>
       <c r="D39" t="s">
         <v>51</v>
@@ -1375,7 +1397,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>45702</v>
       </c>
@@ -1383,7 +1405,7 @@
         <v>7</v>
       </c>
       <c r="C40">
-        <v>0.577873</v>
+        <v>0.57787299999999997</v>
       </c>
       <c r="D40" t="s">
         <v>52</v>
@@ -1392,7 +1414,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>45732</v>
       </c>
@@ -1400,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="C41">
-        <v>0.579668</v>
+        <v>0.57966799999999996</v>
       </c>
       <c r="D41" t="s">
         <v>53</v>
@@ -1409,7 +1431,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>45762</v>
       </c>
@@ -1417,7 +1439,7 @@
         <v>7</v>
       </c>
       <c r="C42">
-        <v>0.586601</v>
+        <v>0.58660100000000004</v>
       </c>
       <c r="D42" t="s">
         <v>54</v>
@@ -1426,7 +1448,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>45792</v>
       </c>
@@ -1434,7 +1456,7 @@
         <v>7</v>
       </c>
       <c r="C43">
-        <v>0.574968</v>
+        <v>0.57496800000000003</v>
       </c>
       <c r="D43" t="s">
         <v>55</v>
@@ -1443,7 +1465,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>45822</v>
       </c>
@@ -1460,7 +1482,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>45852</v>
       </c>
@@ -1468,7 +1490,7 @@
         <v>7</v>
       </c>
       <c r="C45">
-        <v>0.566209</v>
+        <v>0.56620899999999996</v>
       </c>
       <c r="D45" t="s">
         <v>57</v>
@@ -1477,7 +1499,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>45882</v>
       </c>
@@ -1485,7 +1507,7 @@
         <v>7</v>
       </c>
       <c r="C46">
-        <v>0.569879</v>
+        <v>0.56987900000000002</v>
       </c>
       <c r="D46" t="s">
         <v>58</v>
@@ -1494,7 +1516,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>45912</v>
       </c>
@@ -1511,7 +1533,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>45942</v>
       </c>
@@ -1519,7 +1541,7 @@
         <v>7</v>
       </c>
       <c r="C48">
-        <v>0.565284</v>
+        <v>0.56528400000000001</v>
       </c>
       <c r="D48" t="s">
         <v>60</v>
@@ -1528,7 +1550,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>45972</v>
       </c>
@@ -1545,7 +1567,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>46002</v>
       </c>
@@ -1553,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="C50">
-        <v>0.567424</v>
+        <v>0.56742400000000004</v>
       </c>
       <c r="D50" t="s">
         <v>62</v>
@@ -1562,7 +1584,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>46032</v>
       </c>
@@ -1579,7 +1601,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>46062</v>
       </c>
@@ -1587,7 +1609,7 @@
         <v>7</v>
       </c>
       <c r="C52">
-        <v>0.580784</v>
+        <v>0.58078399999999997</v>
       </c>
       <c r="D52" t="s">
         <v>64</v>
@@ -1596,7 +1618,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -1604,7 +1626,7 @@
         <v>7</v>
       </c>
       <c r="C53">
-        <v>0.646402</v>
+        <v>0.64640200000000003</v>
       </c>
       <c r="D53" t="s">
         <v>65</v>
@@ -1613,7 +1635,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1621,7 +1643,7 @@
         <v>7</v>
       </c>
       <c r="C54">
-        <v>0.642002</v>
+        <v>0.64200199999999996</v>
       </c>
       <c r="D54" t="s">
         <v>66</v>
@@ -1630,7 +1652,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>44562</v>
       </c>
@@ -1647,7 +1669,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>44592</v>
       </c>
@@ -1655,7 +1677,7 @@
         <v>8</v>
       </c>
       <c r="C56">
-        <v>0.133804</v>
+        <v>0.13380400000000001</v>
       </c>
       <c r="D56" t="s">
         <v>15</v>
@@ -1664,7 +1686,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>44622</v>
       </c>
@@ -1672,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="C57">
-        <v>0.13417</v>
+        <v>0.13417000000000001</v>
       </c>
       <c r="D57" t="s">
         <v>16</v>
@@ -1681,7 +1703,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>44652</v>
       </c>
@@ -1689,7 +1711,7 @@
         <v>8</v>
       </c>
       <c r="C58">
-        <v>0.132953</v>
+        <v>0.13295299999999999</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -1698,7 +1720,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>44682</v>
       </c>
@@ -1706,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="C59">
-        <v>0.132152</v>
+        <v>0.13215199999999999</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -1715,7 +1737,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>44712</v>
       </c>
@@ -1723,7 +1745,7 @@
         <v>8</v>
       </c>
       <c r="C60">
-        <v>0.132068</v>
+        <v>0.13206799999999999</v>
       </c>
       <c r="D60" t="s">
         <v>19</v>
@@ -1732,7 +1754,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>44742</v>
       </c>
@@ -1749,7 +1771,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>44772</v>
       </c>
@@ -1766,7 +1788,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>44802</v>
       </c>
@@ -1774,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="C63">
-        <v>0.131428</v>
+        <v>0.13142799999999999</v>
       </c>
       <c r="D63" t="s">
         <v>22</v>
@@ -1783,7 +1805,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>44832</v>
       </c>
@@ -1791,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="C64">
-        <v>0.12928</v>
+        <v>0.12928000000000001</v>
       </c>
       <c r="D64" t="s">
         <v>23</v>
@@ -1800,7 +1822,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>44862</v>
       </c>
@@ -1808,7 +1830,7 @@
         <v>8</v>
       </c>
       <c r="C65">
-        <v>0.127899</v>
+        <v>0.12789900000000001</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
@@ -1817,7 +1839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>44892</v>
       </c>
@@ -1834,7 +1856,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>44922</v>
       </c>
@@ -1842,7 +1864,7 @@
         <v>8</v>
       </c>
       <c r="C67">
-        <v>0.132589</v>
+        <v>0.13258900000000001</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
@@ -1851,7 +1873,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>44952</v>
       </c>
@@ -1859,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="C68">
-        <v>0.13462</v>
+        <v>0.13461999999999999</v>
       </c>
       <c r="D68" t="s">
         <v>27</v>
@@ -1868,7 +1890,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>44982</v>
       </c>
@@ -1876,7 +1898,7 @@
         <v>8</v>
       </c>
       <c r="C69">
-        <v>0.132998</v>
+        <v>0.13299800000000001</v>
       </c>
       <c r="D69" t="s">
         <v>28</v>
@@ -1885,7 +1907,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>45012</v>
       </c>
@@ -1902,7 +1924,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>45042</v>
       </c>
@@ -1910,7 +1932,7 @@
         <v>8</v>
       </c>
       <c r="C71">
-        <v>0.134113</v>
+        <v>0.13411300000000001</v>
       </c>
       <c r="D71" t="s">
         <v>30</v>
@@ -1919,7 +1941,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>45072</v>
       </c>
@@ -1936,7 +1958,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>45102</v>
       </c>
@@ -1944,7 +1966,7 @@
         <v>8</v>
       </c>
       <c r="C73">
-        <v>0.133359</v>
+        <v>0.13335900000000001</v>
       </c>
       <c r="D73" t="s">
         <v>32</v>
@@ -1953,7 +1975,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>45132</v>
       </c>
@@ -1961,7 +1983,7 @@
         <v>8</v>
       </c>
       <c r="C74">
-        <v>0.132736</v>
+        <v>0.13273599999999999</v>
       </c>
       <c r="D74" t="s">
         <v>33</v>
@@ -1970,7 +1992,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>45162</v>
       </c>
@@ -1978,7 +2000,7 @@
         <v>8</v>
       </c>
       <c r="C75">
-        <v>0.132321</v>
+        <v>0.13232099999999999</v>
       </c>
       <c r="D75" t="s">
         <v>34</v>
@@ -1987,7 +2009,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>45192</v>
       </c>
@@ -2004,7 +2026,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>45222</v>
       </c>
@@ -2012,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="C77">
-        <v>0.136472</v>
+        <v>0.13647200000000001</v>
       </c>
       <c r="D77" t="s">
         <v>36</v>
@@ -2021,7 +2043,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>45252</v>
       </c>
@@ -2029,7 +2051,7 @@
         <v>8</v>
       </c>
       <c r="C78">
-        <v>0.134035</v>
+        <v>0.13403499999999999</v>
       </c>
       <c r="D78" t="s">
         <v>37</v>
@@ -2038,7 +2060,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>45282</v>
       </c>
@@ -2046,7 +2068,7 @@
         <v>8</v>
       </c>
       <c r="C79">
-        <v>0.135874</v>
+        <v>0.13587399999999999</v>
       </c>
       <c r="D79" t="s">
         <v>38</v>
@@ -2055,7 +2077,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>45312</v>
       </c>
@@ -2063,7 +2085,7 @@
         <v>8</v>
       </c>
       <c r="C80">
-        <v>0.136561</v>
+        <v>0.13656099999999999</v>
       </c>
       <c r="D80" t="s">
         <v>39</v>
@@ -2072,7 +2094,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>45342</v>
       </c>
@@ -2080,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="C81">
-        <v>0.136804</v>
+        <v>0.13680400000000001</v>
       </c>
       <c r="D81" t="s">
         <v>40</v>
@@ -2089,7 +2111,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>45372</v>
       </c>
@@ -2097,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="C82">
-        <v>0.138636</v>
+        <v>0.13863600000000001</v>
       </c>
       <c r="D82" t="s">
         <v>41</v>
@@ -2106,7 +2128,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>45402</v>
       </c>
@@ -2123,7 +2145,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>45432</v>
       </c>
@@ -2131,7 +2153,7 @@
         <v>8</v>
       </c>
       <c r="C84">
-        <v>0.136953</v>
+        <v>0.13695299999999999</v>
       </c>
       <c r="D84" t="s">
         <v>43</v>
@@ -2140,7 +2162,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>45462</v>
       </c>
@@ -2148,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="C85">
-        <v>0.136059</v>
+        <v>0.13605900000000001</v>
       </c>
       <c r="D85" t="s">
         <v>44</v>
@@ -2157,7 +2179,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>45492</v>
       </c>
@@ -2174,7 +2196,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>45522</v>
       </c>
@@ -2182,7 +2204,7 @@
         <v>8</v>
       </c>
       <c r="C87">
-        <v>0.135249</v>
+        <v>0.13524900000000001</v>
       </c>
       <c r="D87" t="s">
         <v>46</v>
@@ -2191,7 +2213,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>45552</v>
       </c>
@@ -2208,7 +2230,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>45582</v>
       </c>
@@ -2225,7 +2247,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>45612</v>
       </c>
@@ -2233,7 +2255,7 @@
         <v>8</v>
       </c>
       <c r="C90">
-        <v>0.133836</v>
+        <v>0.13383600000000001</v>
       </c>
       <c r="D90" t="s">
         <v>49</v>
@@ -2242,7 +2264,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>45642</v>
       </c>
@@ -2259,7 +2281,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>45672</v>
       </c>
@@ -2267,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="C92">
-        <v>0.136788</v>
+        <v>0.13678799999999999</v>
       </c>
       <c r="D92" t="s">
         <v>51</v>
@@ -2276,7 +2298,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>45702</v>
       </c>
@@ -2284,7 +2306,7 @@
         <v>8</v>
       </c>
       <c r="C93">
-        <v>0.135421</v>
+        <v>0.13542100000000001</v>
       </c>
       <c r="D93" t="s">
         <v>52</v>
@@ -2293,7 +2315,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>45732</v>
       </c>
@@ -2310,7 +2332,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>45762</v>
       </c>
@@ -2318,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="C95">
-        <v>0.135895</v>
+        <v>0.13589499999999999</v>
       </c>
       <c r="D95" t="s">
         <v>54</v>
@@ -2327,7 +2349,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>45792</v>
       </c>
@@ -2335,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="C96">
-        <v>0.137725</v>
+        <v>0.13772499999999999</v>
       </c>
       <c r="D96" t="s">
         <v>55</v>
@@ -2344,7 +2366,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>45822</v>
       </c>
@@ -2352,7 +2374,7 @@
         <v>8</v>
       </c>
       <c r="C97">
-        <v>0.139606</v>
+        <v>0.13960600000000001</v>
       </c>
       <c r="D97" t="s">
         <v>56</v>
@@ -2361,7 +2383,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>45852</v>
       </c>
@@ -2369,7 +2391,7 @@
         <v>8</v>
       </c>
       <c r="C98">
-        <v>0.138948</v>
+        <v>0.13894799999999999</v>
       </c>
       <c r="D98" t="s">
         <v>57</v>
@@ -2378,7 +2400,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>45882</v>
       </c>
@@ -2395,7 +2417,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>45912</v>
       </c>
@@ -2403,7 +2425,7 @@
         <v>8</v>
       </c>
       <c r="C100">
-        <v>0.136804</v>
+        <v>0.13680400000000001</v>
       </c>
       <c r="D100" t="s">
         <v>59</v>
@@ -2412,7 +2434,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>45942</v>
       </c>
@@ -2420,7 +2442,7 @@
         <v>8</v>
       </c>
       <c r="C101">
-        <v>0.139364</v>
+        <v>0.13936399999999999</v>
       </c>
       <c r="D101" t="s">
         <v>60</v>
@@ -2429,7 +2451,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>45972</v>
       </c>
@@ -2437,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="C102">
-        <v>0.140785</v>
+        <v>0.14078499999999999</v>
       </c>
       <c r="D102" t="s">
         <v>61</v>
@@ -2446,7 +2468,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>46002</v>
       </c>
@@ -2463,7 +2485,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>46032</v>
       </c>
@@ -2471,7 +2493,7 @@
         <v>8</v>
       </c>
       <c r="C104">
-        <v>0.142023</v>
+        <v>0.14202300000000001</v>
       </c>
       <c r="D104" t="s">
         <v>63</v>
@@ -2480,7 +2502,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>46062</v>
       </c>
@@ -2488,7 +2510,7 @@
         <v>8</v>
       </c>
       <c r="C105">
-        <v>0.1402</v>
+        <v>0.14019999999999999</v>
       </c>
       <c r="D105" t="s">
         <v>64</v>
@@ -2497,7 +2519,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -2505,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="C106">
-        <v>0.13432</v>
+        <v>0.13431999999999999</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -2514,7 +2536,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>6</v>
       </c>
@@ -2522,7 +2544,7 @@
         <v>8</v>
       </c>
       <c r="C107">
-        <v>0.134345</v>
+        <v>0.13434499999999999</v>
       </c>
       <c r="D107" t="s">
         <v>66</v>
@@ -2531,7 +2553,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>44562</v>
       </c>
@@ -2548,7 +2570,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>44592</v>
       </c>
@@ -2565,7 +2587,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>44622</v>
       </c>
@@ -2573,7 +2595,7 @@
         <v>9</v>
       </c>
       <c r="C110">
-        <v>1.07478</v>
+        <v>1.0747800000000001</v>
       </c>
       <c r="D110" t="s">
         <v>16</v>
@@ -2582,7 +2604,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>44652</v>
       </c>
@@ -2599,7 +2621,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>44682</v>
       </c>
@@ -2607,7 +2629,7 @@
         <v>9</v>
       </c>
       <c r="C112">
-        <v>1.083212</v>
+        <v>1.0832120000000001</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
@@ -2616,7 +2638,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A113" s="1">
         <v>44712</v>
       </c>
@@ -2624,7 +2646,7 @@
         <v>9</v>
       </c>
       <c r="C113">
-        <v>1.062663</v>
+        <v>1.0626629999999999</v>
       </c>
       <c r="D113" t="s">
         <v>19</v>
@@ -2633,7 +2655,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A114" s="1">
         <v>44742</v>
       </c>
@@ -2641,7 +2663,7 @@
         <v>9</v>
       </c>
       <c r="C114">
-        <v>1.070969</v>
+        <v>1.0709690000000001</v>
       </c>
       <c r="D114" t="s">
         <v>20</v>
@@ -2650,7 +2672,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A115" s="1">
         <v>44772</v>
       </c>
@@ -2658,7 +2680,7 @@
         <v>9</v>
       </c>
       <c r="C115">
-        <v>1.065481</v>
+        <v>1.0654809999999999</v>
       </c>
       <c r="D115" t="s">
         <v>21</v>
@@ -2667,7 +2689,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A116" s="1">
         <v>44802</v>
       </c>
@@ -2675,7 +2697,7 @@
         <v>9</v>
       </c>
       <c r="C116">
-        <v>1.060153</v>
+        <v>1.0601529999999999</v>
       </c>
       <c r="D116" t="s">
         <v>22</v>
@@ -2684,7 +2706,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A117" s="1">
         <v>44832</v>
       </c>
@@ -2701,7 +2723,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A118" s="1">
         <v>44862</v>
       </c>
@@ -2709,7 +2731,7 @@
         <v>9</v>
       </c>
       <c r="C118">
-        <v>1.039856</v>
+        <v>1.0398559999999999</v>
       </c>
       <c r="D118" t="s">
         <v>24</v>
@@ -2718,7 +2740,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A119" s="1">
         <v>44892</v>
       </c>
@@ -2726,7 +2748,7 @@
         <v>9</v>
       </c>
       <c r="C119">
-        <v>1.023351</v>
+        <v>1.0233509999999999</v>
       </c>
       <c r="D119" t="s">
         <v>25</v>
@@ -2735,7 +2757,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A120" s="1">
         <v>44922</v>
       </c>
@@ -2743,7 +2765,7 @@
         <v>9</v>
       </c>
       <c r="C120">
-        <v>1.028588</v>
+        <v>1.0285880000000001</v>
       </c>
       <c r="D120" t="s">
         <v>26</v>
@@ -2752,7 +2774,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A121" s="1">
         <v>44952</v>
       </c>
@@ -2769,7 +2791,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A122" s="1">
         <v>44982</v>
       </c>
@@ -2786,7 +2808,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A123" s="1">
         <v>45012</v>
       </c>
@@ -2803,7 +2825,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A124" s="1">
         <v>45042</v>
       </c>
@@ -2820,7 +2842,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A125" s="1">
         <v>45072</v>
       </c>
@@ -2837,7 +2859,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A126" s="1">
         <v>45102</v>
       </c>
@@ -2845,7 +2867,7 @@
         <v>9</v>
       </c>
       <c r="C126">
-        <v>1.024045</v>
+        <v>1.0240450000000001</v>
       </c>
       <c r="D126" t="s">
         <v>32</v>
@@ -2854,7 +2876,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A127" s="1">
         <v>45132</v>
       </c>
@@ -2862,7 +2884,7 @@
         <v>9</v>
       </c>
       <c r="C127">
-        <v>1.025902</v>
+        <v>1.0259020000000001</v>
       </c>
       <c r="D127" t="s">
         <v>33</v>
@@ -2871,7 +2893,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A128" s="1">
         <v>45162</v>
       </c>
@@ -2888,7 +2910,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A129" s="1">
         <v>45192</v>
       </c>
@@ -2905,7 +2927,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A130" s="1">
         <v>45222</v>
       </c>
@@ -2913,7 +2935,7 @@
         <v>9</v>
       </c>
       <c r="C130">
-        <v>1.023486</v>
+        <v>1.0234859999999999</v>
       </c>
       <c r="D130" t="s">
         <v>36</v>
@@ -2922,7 +2944,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A131" s="1">
         <v>45252</v>
       </c>
@@ -2930,7 +2952,7 @@
         <v>9</v>
       </c>
       <c r="C131">
-        <v>1.020811</v>
+        <v>1.0208109999999999</v>
       </c>
       <c r="D131" t="s">
         <v>37</v>
@@ -2939,7 +2961,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A132" s="1">
         <v>45282</v>
       </c>
@@ -2947,7 +2969,7 @@
         <v>9</v>
       </c>
       <c r="C132">
-        <v>1.040463</v>
+        <v>1.0404629999999999</v>
       </c>
       <c r="D132" t="s">
         <v>38</v>
@@ -2956,7 +2978,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A133" s="1">
         <v>45312</v>
       </c>
@@ -2964,7 +2986,7 @@
         <v>9</v>
       </c>
       <c r="C133">
-        <v>1.050388</v>
+        <v>1.0503880000000001</v>
       </c>
       <c r="D133" t="s">
         <v>39</v>
@@ -2973,7 +2995,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A134" s="1">
         <v>45342</v>
       </c>
@@ -2981,7 +3003,7 @@
         <v>9</v>
       </c>
       <c r="C134">
-        <v>1.049916</v>
+        <v>1.0499160000000001</v>
       </c>
       <c r="D134" t="s">
         <v>40</v>
@@ -2990,7 +3012,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A135" s="1">
         <v>45372</v>
       </c>
@@ -3007,7 +3029,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A136" s="1">
         <v>45402</v>
       </c>
@@ -3015,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="C136">
-        <v>1.050461</v>
+        <v>1.0504610000000001</v>
       </c>
       <c r="D136" t="s">
         <v>42</v>
@@ -3024,7 +3046,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A137" s="1">
         <v>45432</v>
       </c>
@@ -3032,7 +3054,7 @@
         <v>9</v>
       </c>
       <c r="C137">
-        <v>1.041918</v>
+        <v>1.0419179999999999</v>
       </c>
       <c r="D137" t="s">
         <v>43</v>
@@ -3041,7 +3063,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A138" s="1">
         <v>45462</v>
       </c>
@@ -3058,7 +3080,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A139" s="1">
         <v>45492</v>
       </c>
@@ -3075,7 +3097,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A140" s="1">
         <v>45522</v>
       </c>
@@ -3083,7 +3105,7 @@
         <v>9</v>
       </c>
       <c r="C140">
-        <v>1.006361</v>
+        <v>1.0063610000000001</v>
       </c>
       <c r="D140" t="s">
         <v>46</v>
@@ -3092,7 +3114,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A141" s="1">
         <v>45552</v>
       </c>
@@ -3100,7 +3122,7 @@
         <v>9</v>
       </c>
       <c r="C141">
-        <v>1.004938</v>
+        <v>1.0049380000000001</v>
       </c>
       <c r="D141" t="s">
         <v>47</v>
@@ -3109,7 +3131,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A142" s="1">
         <v>45582</v>
       </c>
@@ -3117,7 +3139,7 @@
         <v>9</v>
       </c>
       <c r="C142">
-        <v>0.990375</v>
+        <v>0.99037500000000001</v>
       </c>
       <c r="D142" t="s">
         <v>48</v>
@@ -3126,7 +3148,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A143" s="1">
         <v>45612</v>
       </c>
@@ -3143,7 +3165,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A144" s="1">
         <v>45642</v>
       </c>
@@ -3151,7 +3173,7 @@
         <v>9</v>
       </c>
       <c r="C144">
-        <v>1.007141</v>
+        <v>1.0071410000000001</v>
       </c>
       <c r="D144" t="s">
         <v>50</v>
@@ -3160,7 +3182,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A145" s="1">
         <v>45672</v>
       </c>
@@ -3168,7 +3190,7 @@
         <v>9</v>
       </c>
       <c r="C145">
-        <v>0.99834</v>
+        <v>0.99834000000000001</v>
       </c>
       <c r="D145" t="s">
         <v>51</v>
@@ -3177,7 +3199,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A146" s="1">
         <v>45702</v>
       </c>
@@ -3185,7 +3207,7 @@
         <v>9</v>
       </c>
       <c r="C146">
-        <v>1.00158</v>
+        <v>1.0015799999999999</v>
       </c>
       <c r="D146" t="s">
         <v>52</v>
@@ -3194,7 +3216,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A147" s="1">
         <v>45732</v>
       </c>
@@ -3211,7 +3233,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A148" s="1">
         <v>45762</v>
       </c>
@@ -3219,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="C148">
-        <v>1.011073</v>
+        <v>1.0110730000000001</v>
       </c>
       <c r="D148" t="s">
         <v>54</v>
@@ -3228,7 +3250,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A149" s="1">
         <v>45792</v>
       </c>
@@ -3236,7 +3258,7 @@
         <v>9</v>
       </c>
       <c r="C149">
-        <v>1.027124</v>
+        <v>1.0271239999999999</v>
       </c>
       <c r="D149" t="s">
         <v>55</v>
@@ -3245,7 +3267,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A150" s="1">
         <v>45822</v>
       </c>
@@ -3262,7 +3284,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A151" s="1">
         <v>45852</v>
       </c>
@@ -3270,7 +3292,7 @@
         <v>9</v>
       </c>
       <c r="C151">
-        <v>0.995711</v>
+        <v>0.99571100000000001</v>
       </c>
       <c r="D151" t="s">
         <v>57</v>
@@ -3279,7 +3301,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A152" s="1">
         <v>45882</v>
       </c>
@@ -3287,7 +3309,7 @@
         <v>9</v>
       </c>
       <c r="C152">
-        <v>1.004161</v>
+        <v>1.0041610000000001</v>
       </c>
       <c r="D152" t="s">
         <v>58</v>
@@ -3296,7 +3318,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A153" s="1">
         <v>45912</v>
       </c>
@@ -3304,7 +3326,7 @@
         <v>9</v>
       </c>
       <c r="C153">
-        <v>1.009627</v>
+        <v>1.0096270000000001</v>
       </c>
       <c r="D153" t="s">
         <v>59</v>
@@ -3313,7 +3335,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A154" s="1">
         <v>45942</v>
       </c>
@@ -3321,7 +3343,7 @@
         <v>9</v>
       </c>
       <c r="C154">
-        <v>0.997328</v>
+        <v>0.99732799999999999</v>
       </c>
       <c r="D154" t="s">
         <v>60</v>
@@ -3330,7 +3352,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A155" s="1">
         <v>45972</v>
       </c>
@@ -3347,7 +3369,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A156" s="1">
         <v>46002</v>
       </c>
@@ -3355,7 +3377,7 @@
         <v>9</v>
       </c>
       <c r="C156">
-        <v>0.997911</v>
+        <v>0.99791099999999999</v>
       </c>
       <c r="D156" t="s">
         <v>62</v>
@@ -3364,7 +3386,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A157" s="1">
         <v>46032</v>
       </c>
@@ -3372,7 +3394,7 @@
         <v>9</v>
       </c>
       <c r="C157">
-        <v>0.997621</v>
+        <v>0.99762099999999998</v>
       </c>
       <c r="D157" t="s">
         <v>63</v>
@@ -3381,7 +3403,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A158" s="1">
         <v>46062</v>
       </c>
@@ -3389,7 +3411,7 @@
         <v>9</v>
       </c>
       <c r="C158">
-        <v>0.998486</v>
+        <v>0.99848599999999998</v>
       </c>
       <c r="D158" t="s">
         <v>64</v>
@@ -3398,7 +3420,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -3415,7 +3437,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -3423,7 +3445,7 @@
         <v>9</v>
       </c>
       <c r="C160">
-        <v>1.071381</v>
+        <v>1.0713809999999999</v>
       </c>
       <c r="D160" t="s">
         <v>66</v>
@@ -3432,7 +3454,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A161" s="1">
         <v>44562</v>
       </c>
@@ -3440,7 +3462,7 @@
         <v>10</v>
       </c>
       <c r="C161">
-        <v>1.247364</v>
+        <v>1.2473639999999999</v>
       </c>
       <c r="D161" t="s">
         <v>14</v>
@@ -3449,7 +3471,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A162" s="1">
         <v>44592</v>
       </c>
@@ -3466,7 +3488,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A163" s="1">
         <v>44622</v>
       </c>
@@ -3474,7 +3496,7 @@
         <v>10</v>
       </c>
       <c r="C163">
-        <v>1.2712</v>
+        <v>1.2712000000000001</v>
       </c>
       <c r="D163" t="s">
         <v>16</v>
@@ -3483,7 +3505,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A164" s="1">
         <v>44652</v>
       </c>
@@ -3500,7 +3522,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A165" s="1">
         <v>44682</v>
       </c>
@@ -3517,7 +3539,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A166" s="1">
         <v>44712</v>
       </c>
@@ -3525,7 +3547,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>1.256673</v>
+        <v>1.2566729999999999</v>
       </c>
       <c r="D166" t="s">
         <v>19</v>
@@ -3534,7 +3556,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A167" s="1">
         <v>44742</v>
       </c>
@@ -3551,7 +3573,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A168" s="1">
         <v>44772</v>
       </c>
@@ -3559,7 +3581,7 @@
         <v>10</v>
       </c>
       <c r="C168">
-        <v>1.259291</v>
+        <v>1.2592909999999999</v>
       </c>
       <c r="D168" t="s">
         <v>21</v>
@@ -3568,7 +3590,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A169" s="1">
         <v>44802</v>
       </c>
@@ -3585,7 +3607,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A170" s="1">
         <v>44832</v>
       </c>
@@ -3593,7 +3615,7 @@
         <v>10</v>
       </c>
       <c r="C170">
-        <v>1.246285</v>
+        <v>1.2462850000000001</v>
       </c>
       <c r="D170" t="s">
         <v>23</v>
@@ -3602,7 +3624,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A171" s="1">
         <v>44862</v>
       </c>
@@ -3610,7 +3632,7 @@
         <v>10</v>
       </c>
       <c r="C171">
-        <v>1.251483</v>
+        <v>1.2514829999999999</v>
       </c>
       <c r="D171" t="s">
         <v>24</v>
@@ -3619,7 +3641,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A172" s="1">
         <v>44892</v>
       </c>
@@ -3627,7 +3649,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>1.266442</v>
+        <v>1.2664420000000001</v>
       </c>
       <c r="D172" t="s">
         <v>25</v>
@@ -3636,7 +3658,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A173" s="1">
         <v>44922</v>
       </c>
@@ -3644,7 +3666,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>1.254684</v>
+        <v>1.2546839999999999</v>
       </c>
       <c r="D173" t="s">
         <v>26</v>
@@ -3653,7 +3675,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A174" s="1">
         <v>44952</v>
       </c>
@@ -3670,7 +3692,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A175" s="1">
         <v>44982</v>
       </c>
@@ -3678,7 +3700,7 @@
         <v>10</v>
       </c>
       <c r="C175">
-        <v>1.265931</v>
+        <v>1.2659309999999999</v>
       </c>
       <c r="D175" t="s">
         <v>28</v>
@@ -3687,7 +3709,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A176" s="1">
         <v>45012</v>
       </c>
@@ -3704,7 +3726,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A177" s="1">
         <v>45042</v>
       </c>
@@ -3721,7 +3743,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A178" s="1">
         <v>45072</v>
       </c>
@@ -3738,7 +3760,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A179" s="1">
         <v>45102</v>
       </c>
@@ -3755,7 +3777,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A180" s="1">
         <v>45132</v>
       </c>
@@ -3763,7 +3785,7 @@
         <v>10</v>
       </c>
       <c r="C180">
-        <v>1.276145</v>
+        <v>1.2761450000000001</v>
       </c>
       <c r="D180" t="s">
         <v>33</v>
@@ -3772,7 +3794,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A181" s="1">
         <v>45162</v>
       </c>
@@ -3780,7 +3802,7 @@
         <v>10</v>
       </c>
       <c r="C181">
-        <v>1.273198</v>
+        <v>1.2731980000000001</v>
       </c>
       <c r="D181" t="s">
         <v>34</v>
@@ -3789,7 +3811,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A182" s="1">
         <v>45192</v>
       </c>
@@ -3806,7 +3828,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A183" s="1">
         <v>45222</v>
       </c>
@@ -3823,7 +3845,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A184" s="1">
         <v>45252</v>
       </c>
@@ -3831,7 +3853,7 @@
         <v>10</v>
       </c>
       <c r="C184">
-        <v>1.265785</v>
+        <v>1.2657849999999999</v>
       </c>
       <c r="D184" t="s">
         <v>37</v>
@@ -3840,7 +3862,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A185" s="1">
         <v>45282</v>
       </c>
@@ -3857,7 +3879,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A186" s="1">
         <v>45312</v>
       </c>
@@ -3874,7 +3896,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A187" s="1">
         <v>45342</v>
       </c>
@@ -3891,7 +3913,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A188" s="1">
         <v>45372</v>
       </c>
@@ -3908,7 +3930,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A189" s="1">
         <v>45402</v>
       </c>
@@ -3916,7 +3938,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>1.282407</v>
+        <v>1.2824070000000001</v>
       </c>
       <c r="D189" t="s">
         <v>42</v>
@@ -3925,7 +3947,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A190" s="1">
         <v>45432</v>
       </c>
@@ -3942,7 +3964,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A191" s="1">
         <v>45462</v>
       </c>
@@ -3950,7 +3972,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>1.285772</v>
+        <v>1.2857719999999999</v>
       </c>
       <c r="D191" t="s">
         <v>44</v>
@@ -3959,7 +3981,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A192" s="1">
         <v>45492</v>
       </c>
@@ -3976,7 +3998,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A193" s="1">
         <v>45522</v>
       </c>
@@ -3984,7 +4006,7 @@
         <v>10</v>
       </c>
       <c r="C193">
-        <v>1.275964</v>
+        <v>1.2759640000000001</v>
       </c>
       <c r="D193" t="s">
         <v>46</v>
@@ -3993,7 +4015,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A194" s="1">
         <v>45552</v>
       </c>
@@ -4001,7 +4023,7 @@
         <v>10</v>
       </c>
       <c r="C194">
-        <v>1.265135</v>
+        <v>1.2651349999999999</v>
       </c>
       <c r="D194" t="s">
         <v>47</v>
@@ -4010,7 +4032,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A195" s="1">
         <v>45582</v>
       </c>
@@ -4027,7 +4049,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A196" s="1">
         <v>45612</v>
       </c>
@@ -4035,7 +4057,7 @@
         <v>10</v>
       </c>
       <c r="C196">
-        <v>1.260255</v>
+        <v>1.2602549999999999</v>
       </c>
       <c r="D196" t="s">
         <v>49</v>
@@ -4044,7 +4066,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A197" s="1">
         <v>45642</v>
       </c>
@@ -4061,7 +4083,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A198" s="1">
         <v>45672</v>
       </c>
@@ -4078,7 +4100,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A199" s="1">
         <v>45702</v>
       </c>
@@ -4095,7 +4117,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A200" s="1">
         <v>45732</v>
       </c>
@@ -4112,7 +4134,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A201" s="1">
         <v>45762</v>
       </c>
@@ -4120,7 +4142,7 @@
         <v>10</v>
       </c>
       <c r="C201">
-        <v>1.289495</v>
+        <v>1.2894950000000001</v>
       </c>
       <c r="D201" t="s">
         <v>54</v>
@@ -4129,7 +4151,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A202" s="1">
         <v>45792</v>
       </c>
@@ -4146,7 +4168,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A203" s="1">
         <v>45822</v>
       </c>
@@ -4163,7 +4185,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A204" s="1">
         <v>45852</v>
       </c>
@@ -4171,7 +4193,7 @@
         <v>10</v>
       </c>
       <c r="C204">
-        <v>1.266641</v>
+        <v>1.2666409999999999</v>
       </c>
       <c r="D204" t="s">
         <v>57</v>
@@ -4180,7 +4202,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A205" s="1">
         <v>45882</v>
       </c>
@@ -4197,7 +4219,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A206" s="1">
         <v>45912</v>
       </c>
@@ -4205,7 +4227,7 @@
         <v>10</v>
       </c>
       <c r="C206">
-        <v>1.265923</v>
+        <v>1.2659229999999999</v>
       </c>
       <c r="D206" t="s">
         <v>59</v>
@@ -4214,7 +4236,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A207" s="1">
         <v>45942</v>
       </c>
@@ -4222,7 +4244,7 @@
         <v>10</v>
       </c>
       <c r="C207">
-        <v>1.251534</v>
+        <v>1.2515339999999999</v>
       </c>
       <c r="D207" t="s">
         <v>60</v>
@@ -4231,7 +4253,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A208" s="1">
         <v>45972</v>
       </c>
@@ -4239,7 +4261,7 @@
         <v>10</v>
       </c>
       <c r="C208">
-        <v>1.25626</v>
+        <v>1.2562599999999999</v>
       </c>
       <c r="D208" t="s">
         <v>61</v>
@@ -4248,7 +4270,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A209" s="1">
         <v>46002</v>
       </c>
@@ -4265,7 +4287,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A210" s="1">
         <v>46032</v>
       </c>
@@ -4273,7 +4295,7 @@
         <v>10</v>
       </c>
       <c r="C210">
-        <v>1.225844</v>
+        <v>1.2258439999999999</v>
       </c>
       <c r="D210" t="s">
         <v>63</v>
@@ -4282,7 +4304,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A211" s="1">
         <v>46062</v>
       </c>
@@ -4299,7 +4321,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A212" t="s">
         <v>5</v>
       </c>
@@ -4307,7 +4329,7 @@
         <v>10</v>
       </c>
       <c r="C212">
-        <v>1.236139</v>
+        <v>1.2361390000000001</v>
       </c>
       <c r="D212" t="s">
         <v>65</v>
@@ -4316,7 +4338,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A213" t="s">
         <v>6</v>
       </c>
@@ -4333,7 +4355,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A214" s="1">
         <v>44562</v>
       </c>
@@ -4341,7 +4363,7 @@
         <v>11</v>
       </c>
       <c r="C214">
-        <v>0.012039</v>
+        <v>1.2038999999999999E-2</v>
       </c>
       <c r="D214" t="s">
         <v>14</v>
@@ -4350,7 +4372,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A215" s="1">
         <v>44592</v>
       </c>
@@ -4358,7 +4380,7 @@
         <v>11</v>
       </c>
       <c r="C215">
-        <v>0.011911</v>
+        <v>1.1911E-2</v>
       </c>
       <c r="D215" t="s">
         <v>15</v>
@@ -4367,7 +4389,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A216" s="1">
         <v>44622</v>
       </c>
@@ -4375,7 +4397,7 @@
         <v>11</v>
       </c>
       <c r="C216">
-        <v>0.011832</v>
+        <v>1.1832000000000001E-2</v>
       </c>
       <c r="D216" t="s">
         <v>16</v>
@@ -4384,7 +4406,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A217" s="1">
         <v>44652</v>
       </c>
@@ -4392,7 +4414,7 @@
         <v>11</v>
       </c>
       <c r="C217">
-        <v>0.011988</v>
+        <v>1.1988E-2</v>
       </c>
       <c r="D217" t="s">
         <v>17</v>
@@ -4401,7 +4423,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A218" s="1">
         <v>44682</v>
       </c>
@@ -4409,7 +4431,7 @@
         <v>11</v>
       </c>
       <c r="C218">
-        <v>0.01197</v>
+        <v>1.197E-2</v>
       </c>
       <c r="D218" t="s">
         <v>18</v>
@@ -4418,7 +4440,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A219" s="1">
         <v>44712</v>
       </c>
@@ -4426,7 +4448,7 @@
         <v>11</v>
       </c>
       <c r="C219">
-        <v>0.012055</v>
+        <v>1.2055E-2</v>
       </c>
       <c r="D219" t="s">
         <v>19</v>
@@ -4435,7 +4457,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A220" s="1">
         <v>44742</v>
       </c>
@@ -4443,7 +4465,7 @@
         <v>11</v>
       </c>
       <c r="C220">
-        <v>0.011818</v>
+        <v>1.1818E-2</v>
       </c>
       <c r="D220" t="s">
         <v>20</v>
@@ -4452,7 +4474,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A221" s="1">
         <v>44772</v>
       </c>
@@ -4460,7 +4482,7 @@
         <v>11</v>
       </c>
       <c r="C221">
-        <v>0.01173</v>
+        <v>1.1730000000000001E-2</v>
       </c>
       <c r="D221" t="s">
         <v>21</v>
@@ -4469,7 +4491,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A222" s="1">
         <v>44802</v>
       </c>
@@ -4477,7 +4499,7 @@
         <v>11</v>
       </c>
       <c r="C222">
-        <v>0.011598</v>
+        <v>1.1598000000000001E-2</v>
       </c>
       <c r="D222" t="s">
         <v>22</v>
@@ -4486,7 +4508,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A223" s="1">
         <v>44832</v>
       </c>
@@ -4494,7 +4516,7 @@
         <v>11</v>
       </c>
       <c r="C223">
-        <v>0.011497</v>
+        <v>1.1497E-2</v>
       </c>
       <c r="D223" t="s">
         <v>23</v>
@@ -4503,7 +4525,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A224" s="1">
         <v>44862</v>
       </c>
@@ -4511,7 +4533,7 @@
         <v>11</v>
       </c>
       <c r="C224">
-        <v>0.011532</v>
+        <v>1.1532000000000001E-2</v>
       </c>
       <c r="D224" t="s">
         <v>24</v>
@@ -4520,7 +4542,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A225" s="1">
         <v>44892</v>
       </c>
@@ -4528,7 +4550,7 @@
         <v>11</v>
       </c>
       <c r="C225">
-        <v>0.011425</v>
+        <v>1.1424999999999999E-2</v>
       </c>
       <c r="D225" t="s">
         <v>25</v>
@@ -4537,7 +4559,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A226" s="1">
         <v>44922</v>
       </c>
@@ -4545,7 +4567,7 @@
         <v>11</v>
       </c>
       <c r="C226">
-        <v>0.011286</v>
+        <v>1.1285999999999999E-2</v>
       </c>
       <c r="D226" t="s">
         <v>26</v>
@@ -4554,7 +4576,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A227" s="1">
         <v>44952</v>
       </c>
@@ -4562,7 +4584,7 @@
         <v>11</v>
       </c>
       <c r="C227">
-        <v>0.011348</v>
+        <v>1.1348E-2</v>
       </c>
       <c r="D227" t="s">
         <v>27</v>
@@ -4571,7 +4593,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A228" s="1">
         <v>44982</v>
       </c>
@@ -4579,7 +4601,7 @@
         <v>11</v>
       </c>
       <c r="C228">
-        <v>0.011395</v>
+        <v>1.1395000000000001E-2</v>
       </c>
       <c r="D228" t="s">
         <v>28</v>
@@ -4588,7 +4610,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A229" s="1">
         <v>45012</v>
       </c>
@@ -4596,7 +4618,7 @@
         <v>11</v>
       </c>
       <c r="C229">
-        <v>0.011603</v>
+        <v>1.1603E-2</v>
       </c>
       <c r="D229" t="s">
         <v>29</v>
@@ -4605,7 +4627,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A230" s="1">
         <v>45042</v>
       </c>
@@ -4613,7 +4635,7 @@
         <v>11</v>
       </c>
       <c r="C230">
-        <v>0.011602</v>
+        <v>1.1601999999999999E-2</v>
       </c>
       <c r="D230" t="s">
         <v>30</v>
@@ -4622,7 +4644,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A231" s="1">
         <v>45072</v>
       </c>
@@ -4630,7 +4652,7 @@
         <v>11</v>
       </c>
       <c r="C231">
-        <v>0.011829</v>
+        <v>1.1828999999999999E-2</v>
       </c>
       <c r="D231" t="s">
         <v>31</v>
@@ -4639,7 +4661,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A232" s="1">
         <v>45102</v>
       </c>
@@ -4647,7 +4669,7 @@
         <v>11</v>
       </c>
       <c r="C232">
-        <v>0.011906</v>
+        <v>1.1906E-2</v>
       </c>
       <c r="D232" t="s">
         <v>32</v>
@@ -4656,7 +4678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A233" s="1">
         <v>45132</v>
       </c>
@@ -4664,7 +4686,7 @@
         <v>11</v>
       </c>
       <c r="C233">
-        <v>0.01173</v>
+        <v>1.1730000000000001E-2</v>
       </c>
       <c r="D233" t="s">
         <v>33</v>
@@ -4673,7 +4695,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A234" s="1">
         <v>45162</v>
       </c>
@@ -4681,7 +4703,7 @@
         <v>11</v>
       </c>
       <c r="C234">
-        <v>0.011765</v>
+        <v>1.1764999999999999E-2</v>
       </c>
       <c r="D234" t="s">
         <v>34</v>
@@ -4690,7 +4712,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A235" s="1">
         <v>45192</v>
       </c>
@@ -4698,7 +4720,7 @@
         <v>11</v>
       </c>
       <c r="C235">
-        <v>0.011704</v>
+        <v>1.1704000000000001E-2</v>
       </c>
       <c r="D235" t="s">
         <v>35</v>
@@ -4707,7 +4729,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A236" s="1">
         <v>45222</v>
       </c>
@@ -4715,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="C236">
-        <v>0.011756</v>
+        <v>1.1756000000000001E-2</v>
       </c>
       <c r="D236" t="s">
         <v>36</v>
@@ -4724,7 +4746,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A237" s="1">
         <v>45252</v>
       </c>
@@ -4732,7 +4754,7 @@
         <v>11</v>
       </c>
       <c r="C237">
-        <v>0.0116</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="D237" t="s">
         <v>37</v>
@@ -4741,7 +4763,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A238" s="1">
         <v>45282</v>
       </c>
@@ -4749,7 +4771,7 @@
         <v>11</v>
       </c>
       <c r="C238">
-        <v>0.011625</v>
+        <v>1.1625E-2</v>
       </c>
       <c r="D238" t="s">
         <v>38</v>
@@ -4758,7 +4780,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A239" s="1">
         <v>45312</v>
       </c>
@@ -4766,7 +4788,7 @@
         <v>11</v>
       </c>
       <c r="C239">
-        <v>0.011543</v>
+        <v>1.1542999999999999E-2</v>
       </c>
       <c r="D239" t="s">
         <v>39</v>
@@ -4775,7 +4797,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A240" s="1">
         <v>45342</v>
       </c>
@@ -4783,7 +4805,7 @@
         <v>11</v>
       </c>
       <c r="C240">
-        <v>0.011591</v>
+        <v>1.1591000000000001E-2</v>
       </c>
       <c r="D240" t="s">
         <v>40</v>
@@ -4792,7 +4814,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A241" s="1">
         <v>45372</v>
       </c>
@@ -4800,7 +4822,7 @@
         <v>11</v>
       </c>
       <c r="C241">
-        <v>0.011596</v>
+        <v>1.1596E-2</v>
       </c>
       <c r="D241" t="s">
         <v>41</v>
@@ -4809,7 +4831,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A242" s="1">
         <v>45402</v>
       </c>
@@ -4817,7 +4839,7 @@
         <v>11</v>
       </c>
       <c r="C242">
-        <v>0.011497</v>
+        <v>1.1497E-2</v>
       </c>
       <c r="D242" t="s">
         <v>42</v>
@@ -4826,7 +4848,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A243" s="1">
         <v>45432</v>
       </c>
@@ -4834,7 +4856,7 @@
         <v>11</v>
       </c>
       <c r="C243">
-        <v>0.011421</v>
+        <v>1.1421000000000001E-2</v>
       </c>
       <c r="D243" t="s">
         <v>43</v>
@@ -4843,7 +4865,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A244" s="1">
         <v>45462</v>
       </c>
@@ -4851,7 +4873,7 @@
         <v>11</v>
       </c>
       <c r="C244">
-        <v>0.011249</v>
+        <v>1.1249E-2</v>
       </c>
       <c r="D244" t="s">
         <v>44</v>
@@ -4860,7 +4882,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A245" s="1">
         <v>45492</v>
       </c>
@@ -4868,7 +4890,7 @@
         <v>11</v>
       </c>
       <c r="C245">
-        <v>0.011247</v>
+        <v>1.1247E-2</v>
       </c>
       <c r="D245" t="s">
         <v>45</v>
@@ -4877,7 +4899,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A246" s="1">
         <v>45522</v>
       </c>
@@ -4885,7 +4907,7 @@
         <v>11</v>
       </c>
       <c r="C246">
-        <v>0.011094</v>
+        <v>1.1094E-2</v>
       </c>
       <c r="D246" t="s">
         <v>46</v>
@@ -4894,7 +4916,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A247" s="1">
         <v>45552</v>
       </c>
@@ -4902,7 +4924,7 @@
         <v>11</v>
       </c>
       <c r="C247">
-        <v>0.011298</v>
+        <v>1.1298000000000001E-2</v>
       </c>
       <c r="D247" t="s">
         <v>47</v>
@@ -4911,7 +4933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A248" s="1">
         <v>45582</v>
       </c>
@@ -4919,7 +4941,7 @@
         <v>11</v>
       </c>
       <c r="C248">
-        <v>0.011293</v>
+        <v>1.1292999999999999E-2</v>
       </c>
       <c r="D248" t="s">
         <v>48</v>
@@ -4928,7 +4950,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A249" s="1">
         <v>45612</v>
       </c>
@@ -4936,7 +4958,7 @@
         <v>11</v>
       </c>
       <c r="C249">
-        <v>0.011422</v>
+        <v>1.1422E-2</v>
       </c>
       <c r="D249" t="s">
         <v>49</v>
@@ -4945,7 +4967,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A250" s="1">
         <v>45642</v>
       </c>
@@ -4953,7 +4975,7 @@
         <v>11</v>
       </c>
       <c r="C250">
-        <v>0.011567</v>
+        <v>1.1566999999999999E-2</v>
       </c>
       <c r="D250" t="s">
         <v>50</v>
@@ -4962,7 +4984,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A251" s="1">
         <v>45672</v>
       </c>
@@ -4970,7 +4992,7 @@
         <v>11</v>
       </c>
       <c r="C251">
-        <v>0.011745</v>
+        <v>1.1745E-2</v>
       </c>
       <c r="D251" t="s">
         <v>51</v>
@@ -4979,7 +5001,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A252" s="1">
         <v>45702</v>
       </c>
@@ -4987,7 +5009,7 @@
         <v>11</v>
       </c>
       <c r="C252">
-        <v>0.011767</v>
+        <v>1.1767E-2</v>
       </c>
       <c r="D252" t="s">
         <v>52</v>
@@ -4996,7 +5018,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A253" s="1">
         <v>45732</v>
       </c>
@@ -5004,7 +5026,7 @@
         <v>11</v>
       </c>
       <c r="C253">
-        <v>0.011573</v>
+        <v>1.1573E-2</v>
       </c>
       <c r="D253" t="s">
         <v>53</v>
@@ -5013,7 +5035,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A254" s="1">
         <v>45762</v>
       </c>
@@ -5021,7 +5043,7 @@
         <v>11</v>
       </c>
       <c r="C254">
-        <v>0.011571</v>
+        <v>1.1571E-2</v>
       </c>
       <c r="D254" t="s">
         <v>54</v>
@@ -5030,7 +5052,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A255" s="1">
         <v>45792</v>
       </c>
@@ -5038,7 +5060,7 @@
         <v>11</v>
       </c>
       <c r="C255">
-        <v>0.011567</v>
+        <v>1.1566999999999999E-2</v>
       </c>
       <c r="D255" t="s">
         <v>55</v>
@@ -5047,7 +5069,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A256" s="1">
         <v>45822</v>
       </c>
@@ -5055,7 +5077,7 @@
         <v>11</v>
       </c>
       <c r="C256">
-        <v>0.011481</v>
+        <v>1.1481E-2</v>
       </c>
       <c r="D256" t="s">
         <v>56</v>
@@ -5064,7 +5086,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A257" s="1">
         <v>45852</v>
       </c>
@@ -5072,7 +5094,7 @@
         <v>11</v>
       </c>
       <c r="C257">
-        <v>0.011686</v>
+        <v>1.1686E-2</v>
       </c>
       <c r="D257" t="s">
         <v>57</v>
@@ -5081,7 +5103,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A258" s="1">
         <v>45882</v>
       </c>
@@ -5089,7 +5111,7 @@
         <v>11</v>
       </c>
       <c r="C258">
-        <v>0.011732</v>
+        <v>1.1731999999999999E-2</v>
       </c>
       <c r="D258" t="s">
         <v>58</v>
@@ -5098,7 +5120,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A259" s="1">
         <v>45912</v>
       </c>
@@ -5106,7 +5128,7 @@
         <v>11</v>
       </c>
       <c r="C259">
-        <v>0.011779</v>
+        <v>1.1779E-2</v>
       </c>
       <c r="D259" t="s">
         <v>59</v>
@@ -5115,7 +5137,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A260" s="1">
         <v>45942</v>
       </c>
@@ -5123,7 +5145,7 @@
         <v>11</v>
       </c>
       <c r="C260">
-        <v>0.011824</v>
+        <v>1.1823999999999999E-2</v>
       </c>
       <c r="D260" t="s">
         <v>60</v>
@@ -5132,7 +5154,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A261" s="1">
         <v>45972</v>
       </c>
@@ -5140,7 +5162,7 @@
         <v>11</v>
       </c>
       <c r="C261">
-        <v>0.011988</v>
+        <v>1.1988E-2</v>
       </c>
       <c r="D261" t="s">
         <v>61</v>
@@ -5149,7 +5171,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A262" s="1">
         <v>46002</v>
       </c>
@@ -5157,7 +5179,7 @@
         <v>11</v>
       </c>
       <c r="C262">
-        <v>0.01209</v>
+        <v>1.209E-2</v>
       </c>
       <c r="D262" t="s">
         <v>62</v>
@@ -5166,7 +5188,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A263" s="1">
         <v>46032</v>
       </c>
@@ -5174,7 +5196,7 @@
         <v>11</v>
       </c>
       <c r="C263">
-        <v>0.012028</v>
+        <v>1.2028E-2</v>
       </c>
       <c r="D263" t="s">
         <v>63</v>
@@ -5183,7 +5205,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A264" s="1">
         <v>46062</v>
       </c>
@@ -5191,7 +5213,7 @@
         <v>11</v>
       </c>
       <c r="C264">
-        <v>0.011819</v>
+        <v>1.1819E-2</v>
       </c>
       <c r="D264" t="s">
         <v>64</v>
@@ -5200,7 +5222,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A265" t="s">
         <v>5</v>
       </c>
@@ -5208,7 +5230,7 @@
         <v>11</v>
       </c>
       <c r="C265">
-        <v>0.011813</v>
+        <v>1.1813000000000001E-2</v>
       </c>
       <c r="D265" t="s">
         <v>65</v>
@@ -5217,7 +5239,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -5225,7 +5247,7 @@
         <v>11</v>
       </c>
       <c r="C266">
-        <v>0.01184</v>
+        <v>1.184E-2</v>
       </c>
       <c r="D266" t="s">
         <v>66</v>
@@ -5234,7 +5256,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A267" s="1">
         <v>44562</v>
       </c>
@@ -5242,7 +5264,7 @@
         <v>12</v>
       </c>
       <c r="C267">
-        <v>0.006786</v>
+        <v>6.7860000000000004E-3</v>
       </c>
       <c r="D267" t="s">
         <v>14</v>
@@ -5251,7 +5273,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A268" s="1">
         <v>44592</v>
       </c>
@@ -5259,7 +5281,7 @@
         <v>12</v>
       </c>
       <c r="C268">
-        <v>0.006806</v>
+        <v>6.8060000000000004E-3</v>
       </c>
       <c r="D268" t="s">
         <v>15</v>
@@ -5268,7 +5290,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A269" s="1">
         <v>44622</v>
       </c>
@@ -5276,7 +5298,7 @@
         <v>12</v>
       </c>
       <c r="C269">
-        <v>0.006734</v>
+        <v>6.7340000000000004E-3</v>
       </c>
       <c r="D269" t="s">
         <v>16</v>
@@ -5285,7 +5307,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A270" s="1">
         <v>44652</v>
       </c>
@@ -5293,7 +5315,7 @@
         <v>12</v>
       </c>
       <c r="C270">
-        <v>0.00664</v>
+        <v>6.6400000000000001E-3</v>
       </c>
       <c r="D270" t="s">
         <v>17</v>
@@ -5302,7 +5324,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A271" s="1">
         <v>44682</v>
       </c>
@@ -5310,7 +5332,7 @@
         <v>12</v>
       </c>
       <c r="C271">
-        <v>0.006721</v>
+        <v>6.7210000000000004E-3</v>
       </c>
       <c r="D271" t="s">
         <v>18</v>
@@ -5319,7 +5341,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A272" s="1">
         <v>44712</v>
       </c>
@@ -5327,7 +5349,7 @@
         <v>12</v>
       </c>
       <c r="C272">
-        <v>0.006702</v>
+        <v>6.7019999999999996E-3</v>
       </c>
       <c r="D272" t="s">
         <v>19</v>
@@ -5336,7 +5358,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A273" s="1">
         <v>44742</v>
       </c>
@@ -5344,7 +5366,7 @@
         <v>12</v>
       </c>
       <c r="C273">
-        <v>0.006649</v>
+        <v>6.6490000000000004E-3</v>
       </c>
       <c r="D273" t="s">
         <v>20</v>
@@ -5353,7 +5375,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A274" s="1">
         <v>44772</v>
       </c>
@@ -5361,7 +5383,7 @@
         <v>12</v>
       </c>
       <c r="C274">
-        <v>0.006587</v>
+        <v>6.587E-3</v>
       </c>
       <c r="D274" t="s">
         <v>21</v>
@@ -5370,7 +5392,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A275" s="1">
         <v>44802</v>
       </c>
@@ -5378,7 +5400,7 @@
         <v>12</v>
       </c>
       <c r="C275">
-        <v>0.006475</v>
+        <v>6.4749999999999999E-3</v>
       </c>
       <c r="D275" t="s">
         <v>22</v>
@@ -5387,7 +5409,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A276" s="1">
         <v>44832</v>
       </c>
@@ -5395,7 +5417,7 @@
         <v>12</v>
       </c>
       <c r="C276">
-        <v>0.006467</v>
+        <v>6.4669999999999997E-3</v>
       </c>
       <c r="D276" t="s">
         <v>23</v>
@@ -5404,7 +5426,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A277" s="1">
         <v>44862</v>
       </c>
@@ -5412,7 +5434,7 @@
         <v>12</v>
       </c>
       <c r="C277">
-        <v>0.006429</v>
+        <v>6.4289999999999998E-3</v>
       </c>
       <c r="D277" t="s">
         <v>24</v>
@@ -5421,7 +5443,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A278" s="1">
         <v>44892</v>
       </c>
@@ -5429,7 +5451,7 @@
         <v>12</v>
       </c>
       <c r="C278">
-        <v>0.006443</v>
+        <v>6.4429999999999999E-3</v>
       </c>
       <c r="D278" t="s">
         <v>25</v>
@@ -5438,7 +5460,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A279" s="1">
         <v>44922</v>
       </c>
@@ -5446,7 +5468,7 @@
         <v>12</v>
       </c>
       <c r="C279">
-        <v>0.006563</v>
+        <v>6.5630000000000003E-3</v>
       </c>
       <c r="D279" t="s">
         <v>26</v>
@@ -5455,7 +5477,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A280" s="1">
         <v>44952</v>
       </c>
@@ -5463,7 +5485,7 @@
         <v>12</v>
       </c>
       <c r="C280">
-        <v>0.006565</v>
+        <v>6.5649999999999997E-3</v>
       </c>
       <c r="D280" t="s">
         <v>27</v>
@@ -5472,7 +5494,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A281" s="1">
         <v>44982</v>
       </c>
@@ -5480,7 +5502,7 @@
         <v>12</v>
       </c>
       <c r="C281">
-        <v>0.006599</v>
+        <v>6.5989999999999998E-3</v>
       </c>
       <c r="D281" t="s">
         <v>28</v>
@@ -5489,7 +5511,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A282" s="1">
         <v>45012</v>
       </c>
@@ -5497,7 +5519,7 @@
         <v>12</v>
       </c>
       <c r="C282">
-        <v>0.00651</v>
+        <v>6.5100000000000002E-3</v>
       </c>
       <c r="D282" t="s">
         <v>29</v>
@@ -5506,7 +5528,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A283" s="1">
         <v>45042</v>
       </c>
@@ -5514,7 +5536,7 @@
         <v>12</v>
       </c>
       <c r="C283">
-        <v>0.006605</v>
+        <v>6.6049999999999998E-3</v>
       </c>
       <c r="D283" t="s">
         <v>30</v>
@@ -5523,7 +5545,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A284" s="1">
         <v>45072</v>
       </c>
@@ -5531,7 +5553,7 @@
         <v>12</v>
       </c>
       <c r="C284">
-        <v>0.006682</v>
+        <v>6.6819999999999996E-3</v>
       </c>
       <c r="D284" t="s">
         <v>31</v>
@@ -5540,7 +5562,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A285" s="1">
         <v>45102</v>
       </c>
@@ -5548,7 +5570,7 @@
         <v>12</v>
       </c>
       <c r="C285">
-        <v>0.006697</v>
+        <v>6.6969999999999998E-3</v>
       </c>
       <c r="D285" t="s">
         <v>32</v>
@@ -5557,7 +5579,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A286" s="1">
         <v>45132</v>
       </c>
@@ -5565,7 +5587,7 @@
         <v>12</v>
       </c>
       <c r="C286">
-        <v>0.006686</v>
+        <v>6.6860000000000001E-3</v>
       </c>
       <c r="D286" t="s">
         <v>33</v>
@@ -5574,7 +5596,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A287" s="1">
         <v>45162</v>
       </c>
@@ -5582,7 +5604,7 @@
         <v>12</v>
       </c>
       <c r="C287">
-        <v>0.006656</v>
+        <v>6.6559999999999996E-3</v>
       </c>
       <c r="D287" t="s">
         <v>34</v>
@@ -5591,7 +5613,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A288" s="1">
         <v>45192</v>
       </c>
@@ -5599,7 +5621,7 @@
         <v>12</v>
       </c>
       <c r="C288">
-        <v>0.00654</v>
+        <v>6.5399999999999998E-3</v>
       </c>
       <c r="D288" t="s">
         <v>35</v>
@@ -5608,7 +5630,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A289" s="1">
         <v>45222</v>
       </c>
@@ -5616,7 +5638,7 @@
         <v>12</v>
       </c>
       <c r="C289">
-        <v>0.006628</v>
+        <v>6.6280000000000002E-3</v>
       </c>
       <c r="D289" t="s">
         <v>36</v>
@@ -5625,7 +5647,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A290" s="1">
         <v>45252</v>
       </c>
@@ -5633,7 +5655,7 @@
         <v>12</v>
       </c>
       <c r="C290">
-        <v>0.00655</v>
+        <v>6.5500000000000003E-3</v>
       </c>
       <c r="D290" t="s">
         <v>37</v>
@@ -5642,7 +5664,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A291" s="1">
         <v>45282</v>
       </c>
@@ -5650,7 +5672,7 @@
         <v>12</v>
       </c>
       <c r="C291">
-        <v>0.00645</v>
+        <v>6.45E-3</v>
       </c>
       <c r="D291" t="s">
         <v>38</v>
@@ -5659,7 +5681,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A292" s="1">
         <v>45312</v>
       </c>
@@ -5667,7 +5689,7 @@
         <v>12</v>
       </c>
       <c r="C292">
-        <v>0.006528</v>
+        <v>6.5279999999999999E-3</v>
       </c>
       <c r="D292" t="s">
         <v>39</v>
@@ -5676,7 +5698,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A293" s="1">
         <v>45342</v>
       </c>
@@ -5684,7 +5706,7 @@
         <v>12</v>
       </c>
       <c r="C293">
-        <v>0.006494</v>
+        <v>6.4939999999999998E-3</v>
       </c>
       <c r="D293" t="s">
         <v>40</v>
@@ -5693,7 +5715,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A294" s="1">
         <v>45372</v>
       </c>
@@ -5701,7 +5723,7 @@
         <v>12</v>
       </c>
       <c r="C294">
-        <v>0.006622</v>
+        <v>6.6220000000000003E-3</v>
       </c>
       <c r="D294" t="s">
         <v>41</v>
@@ -5710,7 +5732,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A295" s="1">
         <v>45402</v>
       </c>
@@ -5718,7 +5740,7 @@
         <v>12</v>
       </c>
       <c r="C295">
-        <v>0.00669</v>
+        <v>6.6899999999999998E-3</v>
       </c>
       <c r="D295" t="s">
         <v>42</v>
@@ -5727,7 +5749,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A296" s="1">
         <v>45432</v>
       </c>
@@ -5735,7 +5757,7 @@
         <v>12</v>
       </c>
       <c r="C296">
-        <v>0.006725</v>
+        <v>6.7250000000000001E-3</v>
       </c>
       <c r="D296" t="s">
         <v>43</v>
@@ -5744,7 +5766,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A297" s="1">
         <v>45462</v>
       </c>
@@ -5752,7 +5774,7 @@
         <v>12</v>
       </c>
       <c r="C297">
-        <v>0.006593</v>
+        <v>6.5929999999999999E-3</v>
       </c>
       <c r="D297" t="s">
         <v>44</v>
@@ -5761,7 +5783,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A298" s="1">
         <v>45492</v>
       </c>
@@ -5769,7 +5791,7 @@
         <v>12</v>
       </c>
       <c r="C298">
-        <v>0.006522</v>
+        <v>6.522E-3</v>
       </c>
       <c r="D298" t="s">
         <v>45</v>
@@ -5778,7 +5800,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A299" s="1">
         <v>45522</v>
       </c>
@@ -5786,7 +5808,7 @@
         <v>12</v>
       </c>
       <c r="C299">
-        <v>0.006451</v>
+        <v>6.4510000000000001E-3</v>
       </c>
       <c r="D299" t="s">
         <v>46</v>
@@ -5795,7 +5817,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A300" s="1">
         <v>45552</v>
       </c>
@@ -5803,7 +5825,7 @@
         <v>12</v>
       </c>
       <c r="C300">
-        <v>0.006356</v>
+        <v>6.3559999999999997E-3</v>
       </c>
       <c r="D300" t="s">
         <v>47</v>
@@ -5812,7 +5834,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A301" s="1">
         <v>45582</v>
       </c>
@@ -5820,7 +5842,7 @@
         <v>12</v>
       </c>
       <c r="C301">
-        <v>0.00625</v>
+        <v>6.2500000000000003E-3</v>
       </c>
       <c r="D301" t="s">
         <v>48</v>
@@ -5829,7 +5851,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A302" s="1">
         <v>45612</v>
       </c>
@@ -5837,7 +5859,7 @@
         <v>12</v>
       </c>
       <c r="C302">
-        <v>0.006238</v>
+        <v>6.2379999999999996E-3</v>
       </c>
       <c r="D302" t="s">
         <v>49</v>
@@ -5846,7 +5868,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A303" s="1">
         <v>45642</v>
       </c>
@@ -5854,7 +5876,7 @@
         <v>12</v>
       </c>
       <c r="C303">
-        <v>0.006229</v>
+        <v>6.2290000000000002E-3</v>
       </c>
       <c r="D303" t="s">
         <v>50</v>
@@ -5863,7 +5885,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A304" s="1">
         <v>45672</v>
       </c>
@@ -5871,7 +5893,7 @@
         <v>12</v>
       </c>
       <c r="C304">
-        <v>0.006162</v>
+        <v>6.1619999999999999E-3</v>
       </c>
       <c r="D304" t="s">
         <v>51</v>
@@ -5880,7 +5902,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A305" s="1">
         <v>45702</v>
       </c>
@@ -5888,7 +5910,7 @@
         <v>12</v>
       </c>
       <c r="C305">
-        <v>0.006259</v>
+        <v>6.2589999999999998E-3</v>
       </c>
       <c r="D305" t="s">
         <v>52</v>
@@ -5897,7 +5919,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A306" s="1">
         <v>45732</v>
       </c>
@@ -5905,7 +5927,7 @@
         <v>12</v>
       </c>
       <c r="C306">
-        <v>0.006351</v>
+        <v>6.3509999999999999E-3</v>
       </c>
       <c r="D306" t="s">
         <v>53</v>
@@ -5914,7 +5936,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A307" s="1">
         <v>45762</v>
       </c>
@@ -5922,7 +5944,7 @@
         <v>12</v>
       </c>
       <c r="C307">
-        <v>0.006331</v>
+        <v>6.3309999999999998E-3</v>
       </c>
       <c r="D307" t="s">
         <v>54</v>
@@ -5931,7 +5953,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A308" s="1">
         <v>45792</v>
       </c>
@@ -5939,7 +5961,7 @@
         <v>12</v>
       </c>
       <c r="C308">
-        <v>0.006268</v>
+        <v>6.2680000000000001E-3</v>
       </c>
       <c r="D308" t="s">
         <v>55</v>
@@ -5948,7 +5970,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A309" s="1">
         <v>45822</v>
       </c>
@@ -5956,7 +5978,7 @@
         <v>12</v>
       </c>
       <c r="C309">
-        <v>0.006265</v>
+        <v>6.2649999999999997E-3</v>
       </c>
       <c r="D309" t="s">
         <v>56</v>
@@ -5965,7 +5987,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A310" s="1">
         <v>45852</v>
       </c>
@@ -5973,7 +5995,7 @@
         <v>12</v>
       </c>
       <c r="C310">
-        <v>0.006306</v>
+        <v>6.306E-3</v>
       </c>
       <c r="D310" t="s">
         <v>57</v>
@@ -5982,7 +6004,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A311" s="1">
         <v>45882</v>
       </c>
@@ -5990,7 +6012,7 @@
         <v>12</v>
       </c>
       <c r="C311">
-        <v>0.00627</v>
+        <v>6.2700000000000004E-3</v>
       </c>
       <c r="D311" t="s">
         <v>58</v>
@@ -5999,7 +6021,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A312" s="1">
         <v>45912</v>
       </c>
@@ -6007,7 +6029,7 @@
         <v>12</v>
       </c>
       <c r="C312">
-        <v>0.006242</v>
+        <v>6.2420000000000002E-3</v>
       </c>
       <c r="D312" t="s">
         <v>59</v>
@@ -6016,7 +6038,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A313" s="1">
         <v>45942</v>
       </c>
@@ -6024,7 +6046,7 @@
         <v>12</v>
       </c>
       <c r="C313">
-        <v>0.006293</v>
+        <v>6.293E-3</v>
       </c>
       <c r="D313" t="s">
         <v>60</v>
@@ -6033,7 +6055,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A314" s="1">
         <v>45972</v>
       </c>
@@ -6041,7 +6063,7 @@
         <v>12</v>
       </c>
       <c r="C314">
-        <v>0.00641</v>
+        <v>6.4099999999999999E-3</v>
       </c>
       <c r="D314" t="s">
         <v>61</v>
@@ -6050,7 +6072,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A315" s="1">
         <v>46002</v>
       </c>
@@ -6058,7 +6080,7 @@
         <v>12</v>
       </c>
       <c r="C315">
-        <v>0.006399</v>
+        <v>6.3990000000000002E-3</v>
       </c>
       <c r="D315" t="s">
         <v>62</v>
@@ -6067,7 +6089,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A316" s="1">
         <v>46032</v>
       </c>
@@ -6075,7 +6097,7 @@
         <v>12</v>
       </c>
       <c r="C316">
-        <v>0.006405</v>
+        <v>6.4050000000000001E-3</v>
       </c>
       <c r="D316" t="s">
         <v>63</v>
@@ -6084,7 +6106,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A317" s="1">
         <v>46062</v>
       </c>
@@ -6092,7 +6114,7 @@
         <v>12</v>
       </c>
       <c r="C317">
-        <v>0.006295</v>
+        <v>6.2950000000000002E-3</v>
       </c>
       <c r="D317" t="s">
         <v>64</v>
@@ -6101,7 +6123,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A318" s="1">
         <v>44562</v>
       </c>
@@ -6109,7 +6131,7 @@
         <v>13</v>
       </c>
       <c r="C318">
-        <v>0.054905</v>
+        <v>5.4905000000000002E-2</v>
       </c>
       <c r="D318" t="s">
         <v>14</v>
@@ -6118,7 +6140,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A319" s="1">
         <v>44592</v>
       </c>
@@ -6126,7 +6148,7 @@
         <v>13</v>
       </c>
       <c r="C319">
-        <v>0.055715</v>
+        <v>5.5715000000000001E-2</v>
       </c>
       <c r="D319" t="s">
         <v>15</v>
@@ -6135,7 +6157,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A320" s="1">
         <v>44622</v>
       </c>
@@ -6143,7 +6165,7 @@
         <v>13</v>
       </c>
       <c r="C320">
-        <v>0.055433</v>
+        <v>5.5433000000000003E-2</v>
       </c>
       <c r="D320" t="s">
         <v>16</v>
@@ -6152,7 +6174,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A321" s="1">
         <v>44652</v>
       </c>
@@ -6160,7 +6182,7 @@
         <v>13</v>
       </c>
       <c r="C321">
-        <v>0.055029</v>
+        <v>5.5029000000000002E-2</v>
       </c>
       <c r="D321" t="s">
         <v>17</v>
@@ -6169,7 +6191,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A322" s="1">
         <v>44682</v>
       </c>
@@ -6177,7 +6199,7 @@
         <v>13</v>
       </c>
       <c r="C322">
-        <v>0.054001</v>
+        <v>5.4001E-2</v>
       </c>
       <c r="D322" t="s">
         <v>18</v>
@@ -6186,7 +6208,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A323" s="1">
         <v>44712</v>
       </c>
@@ -6194,7 +6216,7 @@
         <v>13</v>
       </c>
       <c r="C323">
-        <v>0.052986</v>
+        <v>5.2985999999999998E-2</v>
       </c>
       <c r="D323" t="s">
         <v>19</v>
@@ -6203,7 +6225,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A324" s="1">
         <v>44742</v>
       </c>
@@ -6211,7 +6233,7 @@
         <v>13</v>
       </c>
       <c r="C324">
-        <v>0.052051</v>
+        <v>5.2051E-2</v>
       </c>
       <c r="D324" t="s">
         <v>20</v>
@@ -6220,7 +6242,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A325" s="1">
         <v>44772</v>
       </c>
@@ -6228,7 +6250,7 @@
         <v>13</v>
       </c>
       <c r="C325">
-        <v>0.052497</v>
+        <v>5.2497000000000002E-2</v>
       </c>
       <c r="D325" t="s">
         <v>21</v>
@@ -6237,7 +6259,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A326" s="1">
         <v>44802</v>
       </c>
@@ -6245,7 +6267,7 @@
         <v>13</v>
       </c>
       <c r="C326">
-        <v>0.051658</v>
+        <v>5.1658000000000003E-2</v>
       </c>
       <c r="D326" t="s">
         <v>22</v>
@@ -6254,7 +6276,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A327" s="1">
         <v>44832</v>
       </c>
@@ -6262,7 +6284,7 @@
         <v>13</v>
       </c>
       <c r="C327">
-        <v>0.051253</v>
+        <v>5.1253E-2</v>
       </c>
       <c r="D327" t="s">
         <v>23</v>
@@ -6271,7 +6293,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A328" s="1">
         <v>44862</v>
       </c>
@@ -6279,7 +6301,7 @@
         <v>13</v>
       </c>
       <c r="C328">
-        <v>0.051587</v>
+        <v>5.1587000000000001E-2</v>
       </c>
       <c r="D328" t="s">
         <v>24</v>
@@ -6288,7 +6310,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A329" s="1">
         <v>44892</v>
       </c>
@@ -6296,7 +6318,7 @@
         <v>13</v>
       </c>
       <c r="C329">
-        <v>0.051608</v>
+        <v>5.1608000000000001E-2</v>
       </c>
       <c r="D329" t="s">
         <v>25</v>
@@ -6305,7 +6327,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A330" s="1">
         <v>44922</v>
       </c>
@@ -6313,7 +6335,7 @@
         <v>13</v>
       </c>
       <c r="C330">
-        <v>0.051449</v>
+        <v>5.1449000000000002E-2</v>
       </c>
       <c r="D330" t="s">
         <v>26</v>
@@ -6322,7 +6344,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A331" s="1">
         <v>44952</v>
       </c>
@@ -6330,7 +6352,7 @@
         <v>13</v>
       </c>
       <c r="C331">
-        <v>0.051399</v>
+        <v>5.1399E-2</v>
       </c>
       <c r="D331" t="s">
         <v>27</v>
@@ -6339,7 +6361,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A332" s="1">
         <v>44982</v>
       </c>
@@ -6347,7 +6369,7 @@
         <v>13</v>
       </c>
       <c r="C332">
-        <v>0.051254</v>
+        <v>5.1254000000000001E-2</v>
       </c>
       <c r="D332" t="s">
         <v>28</v>
@@ -6356,7 +6378,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A333" s="1">
         <v>45012</v>
       </c>
@@ -6364,7 +6386,7 @@
         <v>13</v>
       </c>
       <c r="C333">
-        <v>0.050955</v>
+        <v>5.0955E-2</v>
       </c>
       <c r="D333" t="s">
         <v>29</v>
@@ -6373,7 +6395,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A334" s="1">
         <v>45042</v>
       </c>
@@ -6381,7 +6403,7 @@
         <v>13</v>
       </c>
       <c r="C334">
-        <v>0.050639</v>
+        <v>5.0639000000000003E-2</v>
       </c>
       <c r="D334" t="s">
         <v>30</v>
@@ -6390,7 +6412,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A335" s="1">
         <v>45072</v>
       </c>
@@ -6398,7 +6420,7 @@
         <v>13</v>
       </c>
       <c r="C335">
-        <v>0.05017</v>
+        <v>5.0169999999999999E-2</v>
       </c>
       <c r="D335" t="s">
         <v>31</v>
@@ -6407,7 +6429,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A336" s="1">
         <v>45102</v>
       </c>
@@ -6415,7 +6437,7 @@
         <v>13</v>
       </c>
       <c r="C336">
-        <v>0.049909</v>
+        <v>4.9909000000000002E-2</v>
       </c>
       <c r="D336" t="s">
         <v>32</v>
@@ -6424,7 +6446,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A337" s="1">
         <v>45132</v>
       </c>
@@ -6432,7 +6454,7 @@
         <v>13</v>
       </c>
       <c r="C337">
-        <v>0.048985</v>
+        <v>4.8985000000000001E-2</v>
       </c>
       <c r="D337" t="s">
         <v>33</v>
@@ -6441,7 +6463,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A338" s="1">
         <v>45162</v>
       </c>
@@ -6449,7 +6471,7 @@
         <v>13</v>
       </c>
       <c r="C338">
-        <v>0.048729</v>
+        <v>4.8729000000000001E-2</v>
       </c>
       <c r="D338" t="s">
         <v>34</v>
@@ -6458,7 +6480,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A339" s="1">
         <v>45192</v>
       </c>
@@ -6466,7 +6488,7 @@
         <v>13</v>
       </c>
       <c r="C339">
-        <v>0.049064</v>
+        <v>4.9064000000000003E-2</v>
       </c>
       <c r="D339" t="s">
         <v>35</v>
@@ -6475,7 +6497,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A340" s="1">
         <v>45222</v>
       </c>
@@ -6483,7 +6505,7 @@
         <v>13</v>
       </c>
       <c r="C340">
-        <v>0.049758</v>
+        <v>4.9757999999999997E-2</v>
       </c>
       <c r="D340" t="s">
         <v>36</v>
@@ -6492,7 +6514,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A341" s="1">
         <v>45252</v>
       </c>
@@ -6500,7 +6522,7 @@
         <v>13</v>
       </c>
       <c r="C341">
-        <v>0.050335</v>
+        <v>5.0334999999999998E-2</v>
       </c>
       <c r="D341" t="s">
         <v>37</v>
@@ -6509,7 +6531,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A342" s="1">
         <v>45282</v>
       </c>
@@ -6517,7 +6539,7 @@
         <v>13</v>
       </c>
       <c r="C342">
-        <v>0.049351</v>
+        <v>4.9350999999999999E-2</v>
       </c>
       <c r="D342" t="s">
         <v>38</v>
@@ -6526,7 +6548,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A343" s="1">
         <v>45312</v>
       </c>
@@ -6534,7 +6556,7 @@
         <v>13</v>
       </c>
       <c r="C343">
-        <v>0.04968</v>
+        <v>4.9680000000000002E-2</v>
       </c>
       <c r="D343" t="s">
         <v>39</v>
@@ -6543,7 +6565,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A344" s="1">
         <v>45342</v>
       </c>
@@ -6551,7 +6573,7 @@
         <v>13</v>
       </c>
       <c r="C344">
-        <v>0.049132</v>
+        <v>4.9132000000000002E-2</v>
       </c>
       <c r="D344" t="s">
         <v>40</v>
@@ -6560,7 +6582,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A345" s="1">
         <v>45372</v>
       </c>
@@ -6568,7 +6590,7 @@
         <v>13</v>
       </c>
       <c r="C345">
-        <v>0.04868</v>
+        <v>4.8680000000000001E-2</v>
       </c>
       <c r="D345" t="s">
         <v>41</v>
@@ -6577,7 +6599,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A346" s="1">
         <v>45402</v>
       </c>
@@ -6585,7 +6607,7 @@
         <v>13</v>
       </c>
       <c r="C346">
-        <v>0.048061</v>
+        <v>4.8061E-2</v>
       </c>
       <c r="D346" t="s">
         <v>42</v>
@@ -6594,7 +6616,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A347" s="1">
         <v>45432</v>
       </c>
@@ -6602,7 +6624,7 @@
         <v>13</v>
       </c>
       <c r="C347">
-        <v>0.048595</v>
+        <v>4.8594999999999999E-2</v>
       </c>
       <c r="D347" t="s">
         <v>43</v>
@@ -6611,7 +6633,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A348" s="1">
         <v>45462</v>
       </c>
@@ -6619,7 +6641,7 @@
         <v>13</v>
       </c>
       <c r="C348">
-        <v>0.048431</v>
+        <v>4.8431000000000002E-2</v>
       </c>
       <c r="D348" t="s">
         <v>44</v>
@@ -6628,7 +6650,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A349" s="1">
         <v>45492</v>
       </c>
@@ -6636,7 +6658,7 @@
         <v>13</v>
       </c>
       <c r="C349">
-        <v>0.047483</v>
+        <v>4.7482999999999997E-2</v>
       </c>
       <c r="D349" t="s">
         <v>45</v>
@@ -6645,7 +6667,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A350" s="1">
         <v>45522</v>
       </c>
@@ -6653,7 +6675,7 @@
         <v>13</v>
       </c>
       <c r="C350">
-        <v>0.046558</v>
+        <v>4.6558000000000002E-2</v>
       </c>
       <c r="D350" t="s">
         <v>46</v>
@@ -6662,7 +6684,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A351" s="1">
         <v>45552</v>
       </c>
@@ -6670,7 +6692,7 @@
         <v>13</v>
       </c>
       <c r="C351">
-        <v>0.046696</v>
+        <v>4.6696000000000001E-2</v>
       </c>
       <c r="D351" t="s">
         <v>47</v>
@@ -6679,7 +6701,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A352" s="1">
         <v>45582</v>
       </c>
@@ -6687,7 +6709,7 @@
         <v>13</v>
       </c>
       <c r="C352">
-        <v>0.046824</v>
+        <v>4.6823999999999998E-2</v>
       </c>
       <c r="D352" t="s">
         <v>48</v>
@@ -6696,7 +6718,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A353" s="1">
         <v>45612</v>
       </c>
@@ -6704,7 +6726,7 @@
         <v>13</v>
       </c>
       <c r="C353">
-        <v>0.046134</v>
+        <v>4.6134000000000001E-2</v>
       </c>
       <c r="D353" t="s">
         <v>49</v>
@@ -6713,7 +6735,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A354" s="1">
         <v>45642</v>
       </c>
@@ -6721,7 +6743,7 @@
         <v>13</v>
       </c>
       <c r="C354">
-        <v>0.045481</v>
+        <v>4.5481000000000001E-2</v>
       </c>
       <c r="D354" t="s">
         <v>50</v>
@@ -6730,7 +6752,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A355" s="1">
         <v>45672</v>
       </c>
@@ -6738,7 +6760,7 @@
         <v>13</v>
       </c>
       <c r="C355">
-        <v>0.046267</v>
+        <v>4.6267000000000003E-2</v>
       </c>
       <c r="D355" t="s">
         <v>51</v>
@@ -6747,7 +6769,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A356" s="1">
         <v>45702</v>
       </c>
@@ -6755,7 +6777,7 @@
         <v>13</v>
       </c>
       <c r="C356">
-        <v>0.045485</v>
+        <v>4.5484999999999998E-2</v>
       </c>
       <c r="D356" t="s">
         <v>52</v>
@@ -6764,7 +6786,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A357" s="1">
         <v>45732</v>
       </c>
@@ -6772,7 +6794,7 @@
         <v>13</v>
       </c>
       <c r="C357">
-        <v>0.045092</v>
+        <v>4.5092E-2</v>
       </c>
       <c r="D357" t="s">
         <v>53</v>
@@ -6781,7 +6803,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A358" s="1">
         <v>45762</v>
       </c>
@@ -6789,7 +6811,7 @@
         <v>13</v>
       </c>
       <c r="C358">
-        <v>0.045072</v>
+        <v>4.5072000000000001E-2</v>
       </c>
       <c r="D358" t="s">
         <v>54</v>
@@ -6798,7 +6820,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A359" s="1">
         <v>45792</v>
       </c>
@@ -6806,7 +6828,7 @@
         <v>13</v>
       </c>
       <c r="C359">
-        <v>0.044196</v>
+        <v>4.4195999999999999E-2</v>
       </c>
       <c r="D359" t="s">
         <v>55</v>
@@ -6815,7 +6837,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A360" s="1">
         <v>45822</v>
       </c>
@@ -6823,7 +6845,7 @@
         <v>13</v>
       </c>
       <c r="C360">
-        <v>0.043353</v>
+        <v>4.3353000000000003E-2</v>
       </c>
       <c r="D360" t="s">
         <v>56</v>
@@ -6832,7 +6854,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A361" s="1">
         <v>45852</v>
       </c>
@@ -6840,7 +6862,7 @@
         <v>13</v>
       </c>
       <c r="C361">
-        <v>0.04304</v>
+        <v>4.3040000000000002E-2</v>
       </c>
       <c r="D361" t="s">
         <v>57</v>
@@ -6849,7 +6871,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A362" s="1">
         <v>45882</v>
       </c>
@@ -6857,7 +6879,7 @@
         <v>13</v>
       </c>
       <c r="C362">
-        <v>0.043314</v>
+        <v>4.3313999999999998E-2</v>
       </c>
       <c r="D362" t="s">
         <v>58</v>
@@ -6866,7 +6888,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A363" s="1">
         <v>45912</v>
       </c>
@@ -6874,7 +6896,7 @@
         <v>13</v>
       </c>
       <c r="C363">
-        <v>0.042628</v>
+        <v>4.2627999999999999E-2</v>
       </c>
       <c r="D363" t="s">
         <v>59</v>
@@ -6883,7 +6905,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A364" s="1">
         <v>45942</v>
       </c>
@@ -6891,7 +6913,7 @@
         <v>13</v>
       </c>
       <c r="C364">
-        <v>0.041893</v>
+        <v>4.1893E-2</v>
       </c>
       <c r="D364" t="s">
         <v>60</v>
@@ -6900,7 +6922,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A365" s="1">
         <v>45972</v>
       </c>
@@ -6908,7 +6930,7 @@
         <v>13</v>
       </c>
       <c r="C365">
-        <v>0.041308</v>
+        <v>4.1307999999999997E-2</v>
       </c>
       <c r="D365" t="s">
         <v>61</v>
@@ -6917,7 +6939,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A366" s="1">
         <v>46002</v>
       </c>
@@ -6925,7 +6947,7 @@
         <v>13</v>
       </c>
       <c r="C366">
-        <v>0.041091</v>
+        <v>4.1091000000000003E-2</v>
       </c>
       <c r="D366" t="s">
         <v>62</v>
@@ -6934,7 +6956,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A367" s="1">
         <v>46032</v>
       </c>
@@ -6942,7 +6964,7 @@
         <v>13</v>
       </c>
       <c r="C367">
-        <v>0.041878</v>
+        <v>4.1877999999999999E-2</v>
       </c>
       <c r="D367" t="s">
         <v>63</v>
@@ -6951,7 +6973,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A368" s="1">
         <v>46062</v>
       </c>
@@ -6959,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="C368">
-        <v>0.042496</v>
+        <v>4.2495999999999999E-2</v>
       </c>
       <c r="D368" t="s">
         <v>64</v>
@@ -6968,7 +6990,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A369" t="s">
         <v>5</v>
       </c>
@@ -6976,7 +6998,7 @@
         <v>13</v>
       </c>
       <c r="C369">
-        <v>0.054734</v>
+        <v>5.4733999999999998E-2</v>
       </c>
       <c r="D369" t="s">
         <v>65</v>
@@ -6985,7 +7007,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A370" t="s">
         <v>6</v>
       </c>
@@ -6993,7 +7015,7 @@
         <v>13</v>
       </c>
       <c r="C370">
-        <v>0.055766</v>
+        <v>5.5766000000000003E-2</v>
       </c>
       <c r="D370" t="s">
         <v>66</v>
